--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8213-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8213-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D60EF3F-DAB9-4EBF-AFC5-51080C30C264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B660E62D-6F33-4FC9-8A97-883684180C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{71193B5D-A10B-4961-A4D1-83691C89857F}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6A4F75E7-6F4B-4A4F-8CA5-BAC4350B275C}"/>
   </bookViews>
   <sheets>
     <sheet name="8213-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1511,27 +1511,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9D02855-8DC2-4D3D-9421-294299ACB6E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A4AF3A-05C6-49F0-B63B-392C5ACC821C}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1565,7 +1564,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1601,7 +1600,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1653,7 +1652,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1721,7 +1720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1793,7 +1792,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1865,7 +1864,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1937,7 +1936,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -2009,7 +2008,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2081,7 +2080,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2153,7 +2152,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2225,7 +2224,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2297,7 +2296,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2369,7 +2368,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2441,7 +2440,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2513,7 +2512,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2585,7 +2584,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2657,7 +2656,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2729,7 +2728,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2010</v>
       </c>
@@ -2801,7 +2800,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="41"/>
       <c r="B20" s="42"/>
       <c r="C20" s="18" t="s">
@@ -2829,7 +2828,7 @@
       <c r="W20" s="48"/>
       <c r="X20" s="44"/>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2009</v>
       </c>
@@ -2901,7 +2900,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2008</v>
       </c>
@@ -2973,7 +2972,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2007</v>
       </c>
@@ -3045,7 +3044,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2006</v>
       </c>
@@ -3117,7 +3116,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2005</v>
       </c>
@@ -3189,7 +3188,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2004</v>
       </c>
@@ -3261,7 +3260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2003</v>
       </c>
@@ -3333,7 +3332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2001</v>
       </c>
@@ -3405,7 +3404,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>1999</v>
       </c>
@@ -3477,7 +3476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35" t="s">
         <v>51</v>
       </c>
